--- a/uloha28/uloha28.xlsx
+++ b/uloha28/uloha28.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nemec\david\school\praktika\uloha28\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768D2E34-DFA3-49F3-BD33-CA0293EC8806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A44B0351-7630-4C1E-91A2-E4ED5FED4A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{168F654F-1575-4592-821A-2A29CD728C13}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="18">
   <si>
     <t>P/Psun</t>
   </si>
@@ -8152,14 +8152,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>607360</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>450477</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>19948</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>486336</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>430306</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>44825</xdr:rowOff>
     </xdr:to>
@@ -8722,18 +8722,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AD8B240-44C5-4490-B955-C0BB51FDC244}">
-  <dimension ref="A2:R46"/>
+  <dimension ref="A2:S46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.88671875" customWidth="1"/>
     <col min="10" max="10" width="10.33203125" customWidth="1"/>
     <col min="11" max="11" width="8.6640625" customWidth="1"/>
     <col min="12" max="12" width="8.33203125" customWidth="1"/>
-    <col min="14" max="14" width="5.33203125" customWidth="1"/>
+    <col min="14" max="14" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -8756,7 +8757,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>0.1</v>
       </c>
@@ -8767,12 +8768,12 @@
         <v>7.65</v>
       </c>
       <c r="D3">
-        <f>0.00015*B3+2*0.00003</f>
-        <v>1.3192499999999999E-4</v>
+        <f>(1.5*B3+2*0.3)/10000</f>
+        <v>1.3192499999999997E-4</v>
       </c>
       <c r="E3">
-        <f>0.0003*C3+0.00008*200</f>
-        <v>1.8294999999999999E-2</v>
+        <f>(4*C3+2*20)/10000</f>
+        <v>7.0599999999999994E-3</v>
       </c>
       <c r="J3" t="s">
         <v>14</v>
@@ -8786,6 +8787,9 @@
       <c r="M3" t="s">
         <v>15</v>
       </c>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
       <c r="O3" t="s">
         <v>14</v>
       </c>
@@ -8798,8 +8802,11 @@
       <c r="R3" t="s">
         <v>15</v>
       </c>
+      <c r="S3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0.2</v>
       </c>
@@ -8810,12 +8817,12 @@
         <v>17.25</v>
       </c>
       <c r="D4">
-        <f t="shared" ref="D4:D15" si="0">0.00015*B4+2*0.00003</f>
+        <f t="shared" ref="D4:D15" si="0">(1.5*B4+2*0.3)/10000</f>
         <v>1.3664999999999999E-4</v>
       </c>
       <c r="E4">
-        <f t="shared" ref="E4:E15" si="1">0.0003*C4+0.00008*200</f>
-        <v>2.1174999999999999E-2</v>
+        <f t="shared" ref="E4:E15" si="1">(4*C4+2*20)/10000</f>
+        <v>1.09E-2</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -8831,6 +8838,10 @@
         <f>L4*K4*1000</f>
         <v>2.6234884000000003</v>
       </c>
+      <c r="N4">
+        <f>(1.5*K4+0.4*0.2)/10000</f>
+        <v>1.5683000000000002E-5</v>
+      </c>
       <c r="O4">
         <v>1</v>
       </c>
@@ -8845,8 +8856,12 @@
         <f>Q4*P4*1000</f>
         <v>11.79396</v>
       </c>
+      <c r="S4">
+        <f>(1.5*P4+0.4*0.2)/10000</f>
+        <v>2.429E-5</v>
+      </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>0.25</v>
       </c>
@@ -8861,7 +8876,7 @@
         <v>1.3788E-4</v>
       </c>
       <c r="E5">
-        <f t="shared" si="1"/>
+        <f>(3*C5+0.8*200)/10000</f>
         <v>2.2663599999999999E-2</v>
       </c>
       <c r="J5">
@@ -8878,6 +8893,10 @@
         <f t="shared" ref="M5:M23" si="3">L5*K5*1000</f>
         <v>4.8150428444999998</v>
       </c>
+      <c r="N5">
+        <f>(1.5*K5+0.4*0.2)/10000</f>
+        <v>2.2719949999999999E-5</v>
+      </c>
       <c r="O5">
         <v>2</v>
       </c>
@@ -8892,8 +8911,12 @@
         <f t="shared" ref="R5:R21" si="5">Q5*P5*1000</f>
         <v>19.215840799999999</v>
       </c>
+      <c r="S5">
+        <f>(1.5*P5+0.4*0.2)/10000</f>
+        <v>3.7406000000000001E-5</v>
+      </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0.3</v>
       </c>
@@ -8908,7 +8931,7 @@
         <v>1.3885499999999998E-4</v>
       </c>
       <c r="E6">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="E6:E13" si="6">(3*C6+0.8*200)/10000</f>
         <v>2.41648E-2</v>
       </c>
       <c r="J6">
@@ -8925,6 +8948,10 @@
         <f t="shared" si="3"/>
         <v>9.1671050249999979</v>
       </c>
+      <c r="N6">
+        <f>(1.5*K6+0.4*0.2)/10000</f>
+        <v>3.6723500000000002E-5</v>
+      </c>
       <c r="O6">
         <v>3</v>
       </c>
@@ -8939,8 +8966,12 @@
         <f t="shared" si="5"/>
         <v>24.32340563333333</v>
       </c>
+      <c r="S6">
+        <f t="shared" ref="S6:S21" si="7">(1.5*P6+0.3*2)/10000</f>
+        <v>1.0051950000000001E-4</v>
+      </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>0.4</v>
       </c>
@@ -8955,7 +8986,7 @@
         <v>1.4018099999999999E-4</v>
       </c>
       <c r="E7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>2.7142899999999998E-2</v>
       </c>
       <c r="J7">
@@ -8972,6 +9003,10 @@
         <f t="shared" si="3"/>
         <v>13.00886406666667</v>
       </c>
+      <c r="N7">
+        <f>(1.5*K7+0.3*2)/10000</f>
+        <v>1.0190700000000001E-4</v>
+      </c>
       <c r="O7">
         <v>4</v>
       </c>
@@ -8986,8 +9021,12 @@
         <f t="shared" si="5"/>
         <v>27.381975625000003</v>
       </c>
+      <c r="S7">
+        <f t="shared" si="7"/>
+        <v>1.096425E-4</v>
+      </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>0.5</v>
       </c>
@@ -8999,11 +9038,11 @@
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>1.4114999999999999E-4</v>
+        <v>1.4115000000000002E-4</v>
       </c>
       <c r="E8">
-        <f t="shared" si="1"/>
-        <v>3.0126399999999998E-2</v>
+        <f t="shared" si="6"/>
+        <v>3.0126400000000001E-2</v>
       </c>
       <c r="J8">
         <v>8</v>
@@ -9019,6 +9058,10 @@
         <f t="shared" si="3"/>
         <v>15.429096112499998</v>
       </c>
+      <c r="N8">
+        <f t="shared" ref="N8:N23" si="8">(1.5*K8+0.3*2)/10000</f>
+        <v>1.1269949999999999E-4</v>
+      </c>
       <c r="O8">
         <v>5</v>
       </c>
@@ -9033,8 +9076,12 @@
         <f t="shared" si="5"/>
         <v>28.237612499999994</v>
       </c>
+      <c r="S8">
+        <f t="shared" si="7"/>
+        <v>1.1636249999999999E-4</v>
+      </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>0.6</v>
       </c>
@@ -9049,7 +9096,7 @@
         <v>1.41648E-4</v>
       </c>
       <c r="E9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.2986599999999998E-2</v>
       </c>
       <c r="J9">
@@ -9066,6 +9113,10 @@
         <f t="shared" si="3"/>
         <v>15.881880544444446</v>
       </c>
+      <c r="N9">
+        <f t="shared" si="8"/>
+        <v>1.1671049999999998E-4</v>
+      </c>
       <c r="O9">
         <v>6</v>
       </c>
@@ -9080,8 +9131,12 @@
         <f t="shared" si="5"/>
         <v>27.646166399999998</v>
       </c>
+      <c r="S9">
+        <f t="shared" si="7"/>
+        <v>1.2109199999999997E-4</v>
+      </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>0.7</v>
       </c>
@@ -9093,10 +9148,10 @@
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>1.42125E-4</v>
+        <v>1.4212500000000003E-4</v>
       </c>
       <c r="E10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.5793399999999996E-2</v>
       </c>
       <c r="J10">
@@ -9113,6 +9168,10 @@
         <f t="shared" si="3"/>
         <v>15.981605289999999</v>
       </c>
+      <c r="N10">
+        <f t="shared" si="8"/>
+        <v>1.1996549999999999E-4</v>
+      </c>
       <c r="O10">
         <v>7</v>
       </c>
@@ -9127,8 +9186,12 @@
         <f t="shared" si="5"/>
         <v>26.430259557142861</v>
       </c>
+      <c r="S10">
+        <f t="shared" si="7"/>
+        <v>1.2451949999999997E-4</v>
+      </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>0.8</v>
       </c>
@@ -9143,8 +9206,8 @@
         <v>1.4259E-4</v>
       </c>
       <c r="E11">
-        <f t="shared" si="1"/>
-        <v>3.8530599999999998E-2</v>
+        <f t="shared" si="6"/>
+        <v>3.8530600000000005E-2</v>
       </c>
       <c r="J11">
         <v>11</v>
@@ -9160,6 +9223,10 @@
         <f t="shared" si="3"/>
         <v>15.838432727272728</v>
       </c>
+      <c r="N11">
+        <f t="shared" si="8"/>
+        <v>1.2260999999999999E-4</v>
+      </c>
       <c r="O11">
         <v>8</v>
       </c>
@@ -9174,8 +9241,12 @@
         <f t="shared" si="5"/>
         <v>24.963834012500001</v>
       </c>
+      <c r="S11">
+        <f t="shared" si="7"/>
+        <v>1.2703350000000001E-4</v>
+      </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>0.9</v>
       </c>
@@ -9190,8 +9261,8 @@
         <v>1.4291999999999999E-4</v>
       </c>
       <c r="E12">
-        <f t="shared" si="1"/>
-        <v>4.1260599999999995E-2</v>
+        <f t="shared" si="6"/>
+        <v>4.1260600000000001E-2</v>
       </c>
       <c r="J12">
         <v>12</v>
@@ -9207,6 +9278,10 @@
         <f t="shared" si="3"/>
         <v>15.432709633333333</v>
       </c>
+      <c r="N12">
+        <f t="shared" si="8"/>
+        <v>1.2455099999999998E-4</v>
+      </c>
       <c r="O12">
         <v>9</v>
       </c>
@@ -9221,8 +9296,12 @@
         <f t="shared" si="5"/>
         <v>23.437568711111112</v>
       </c>
+      <c r="S12">
+        <f t="shared" si="7"/>
+        <v>1.28892E-4</v>
+      </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1</v>
       </c>
@@ -9234,10 +9313,10 @@
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>1.4295899999999998E-4</v>
+        <v>1.4295900000000001E-4</v>
       </c>
       <c r="E13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>4.37419E-2</v>
       </c>
       <c r="J13">
@@ -9254,6 +9333,10 @@
         <f t="shared" si="3"/>
         <v>14.964826530769232</v>
       </c>
+      <c r="N13">
+        <f t="shared" si="8"/>
+        <v>1.2616049999999998E-4</v>
+      </c>
       <c r="O13">
         <v>10</v>
       </c>
@@ -9268,8 +9351,12 @@
         <f t="shared" si="5"/>
         <v>22.05147681</v>
       </c>
+      <c r="S13">
+        <f t="shared" si="7"/>
+        <v>1.3043849999999998E-4</v>
+      </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>0.12</v>
       </c>
@@ -9285,7 +9372,7 @@
       </c>
       <c r="E14">
         <f t="shared" si="1"/>
-        <v>1.8824799999999999E-2</v>
+        <v>7.7664000000000006E-3</v>
       </c>
       <c r="J14">
         <v>14</v>
@@ -9301,6 +9388,10 @@
         <f t="shared" si="3"/>
         <v>14.470714999999998</v>
       </c>
+      <c r="N14">
+        <f t="shared" si="8"/>
+        <v>1.27515E-4</v>
+      </c>
       <c r="O14">
         <v>11</v>
       </c>
@@ -9315,8 +9406,12 @@
         <f t="shared" si="5"/>
         <v>20.733918627272725</v>
       </c>
+      <c r="S14">
+        <f t="shared" si="7"/>
+        <v>1.3163549999999999E-4</v>
+      </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>0.15</v>
       </c>
@@ -9328,11 +9423,11 @@
       </c>
       <c r="D15">
         <f t="shared" si="0"/>
-        <v>1.3474049999999998E-4</v>
+        <v>1.3474050000000001E-4</v>
       </c>
       <c r="E15">
         <f t="shared" si="1"/>
-        <v>1.9705899999999998E-2</v>
+        <v>8.9411999999999998E-3</v>
       </c>
       <c r="J15">
         <v>15</v>
@@ -9348,6 +9443,10 @@
         <f t="shared" si="3"/>
         <v>13.942772160000001</v>
       </c>
+      <c r="N15">
+        <f t="shared" si="8"/>
+        <v>1.2859799999999998E-4</v>
+      </c>
       <c r="O15">
         <v>15</v>
       </c>
@@ -9362,8 +9461,12 @@
         <f t="shared" si="5"/>
         <v>16.55950614</v>
       </c>
+      <c r="S15">
+        <f t="shared" si="7"/>
+        <v>1.3475849999999999E-4</v>
+      </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="J16">
         <v>20</v>
       </c>
@@ -9378,6 +9481,10 @@
         <f t="shared" si="3"/>
         <v>11.595964820000001</v>
       </c>
+      <c r="N16">
+        <f t="shared" si="8"/>
+        <v>1.3223699999999997E-4</v>
+      </c>
       <c r="O16">
         <v>20</v>
       </c>
@@ -9392,8 +9499,12 @@
         <f t="shared" si="5"/>
         <v>13.109248080000004</v>
       </c>
+      <c r="S16">
+        <f t="shared" si="7"/>
+        <v>1.36806E-4</v>
+      </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="J17">
         <v>25</v>
       </c>
@@ -9408,6 +9519,10 @@
         <f t="shared" si="3"/>
         <v>9.7812099999999997</v>
       </c>
+      <c r="N17">
+        <f t="shared" si="8"/>
+        <v>1.34175E-4</v>
+      </c>
       <c r="O17">
         <v>25</v>
       </c>
@@ -9422,8 +9537,12 @@
         <f t="shared" si="5"/>
         <v>10.828067364000001</v>
       </c>
+      <c r="S17">
+        <f t="shared" si="7"/>
+        <v>1.3804349999999997E-4</v>
+      </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>1</v>
       </c>
@@ -9453,6 +9572,10 @@
         <f t="shared" si="3"/>
         <v>7.3892314999999984</v>
       </c>
+      <c r="N18">
+        <f t="shared" si="8"/>
+        <v>1.362825E-4</v>
+      </c>
       <c r="O18">
         <v>30</v>
       </c>
@@ -9467,8 +9590,12 @@
         <f t="shared" si="5"/>
         <v>9.21061452</v>
       </c>
+      <c r="S18">
+        <f t="shared" si="7"/>
+        <v>1.38849E-4</v>
+      </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -9506,6 +9633,10 @@
         <f t="shared" si="3"/>
         <v>5.908088542222222</v>
       </c>
+      <c r="N19">
+        <f t="shared" si="8"/>
+        <v>1.37343E-4</v>
+      </c>
       <c r="O19">
         <v>40</v>
       </c>
@@ -9520,8 +9651,12 @@
         <f t="shared" si="5"/>
         <v>7.0867764099999997</v>
       </c>
+      <c r="S19">
+        <f t="shared" si="7"/>
+        <v>1.3986299999999997E-4</v>
+      </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -9534,15 +9669,15 @@
         <v>47.088000000000001</v>
       </c>
       <c r="D20">
-        <f t="shared" ref="D20:D21" si="6">B20/C20*1000</f>
+        <f t="shared" ref="D20:D21" si="9">B20/C20*1000</f>
         <v>11.48912674142032</v>
       </c>
       <c r="E20">
-        <f t="shared" ref="E20:E21" si="7">D20/10</f>
+        <f t="shared" ref="E20:E21" si="10">D20/10</f>
         <v>1.1489126741420319</v>
       </c>
       <c r="F20">
-        <f t="shared" ref="F20:F21" si="8">D20*10</f>
+        <f t="shared" ref="F20:F21" si="11">D20*10</f>
         <v>114.8912674142032</v>
       </c>
       <c r="J20">
@@ -9559,6 +9694,10 @@
         <f t="shared" si="3"/>
         <v>12.923988994117645</v>
       </c>
+      <c r="N20">
+        <f t="shared" si="8"/>
+        <v>1.3030949999999998E-4</v>
+      </c>
       <c r="O20">
         <v>50</v>
       </c>
@@ -9573,8 +9712,12 @@
         <f t="shared" si="5"/>
         <v>5.7553574720000009</v>
       </c>
+      <c r="S20">
+        <f t="shared" si="7"/>
+        <v>1.4046600000000001E-4</v>
+      </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -9587,15 +9730,15 @@
         <v>92.472999999999999</v>
       </c>
       <c r="D21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>5.9807727661047014</v>
       </c>
       <c r="E21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0.59807727661047017</v>
       </c>
       <c r="F21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>59.807727661047011</v>
       </c>
       <c r="J21">
@@ -9612,6 +9755,10 @@
         <f t="shared" si="3"/>
         <v>14.490840014285714</v>
       </c>
+      <c r="N21">
+        <f t="shared" si="8"/>
+        <v>1.0777350000000001E-4</v>
+      </c>
       <c r="O21">
         <v>60</v>
       </c>
@@ -9626,8 +9773,12 @@
         <f t="shared" si="5"/>
         <v>4.8350122016666663</v>
       </c>
+      <c r="S21">
+        <f t="shared" si="7"/>
+        <v>1.4079150000000001E-4</v>
+      </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="J22">
         <v>55</v>
       </c>
@@ -9642,8 +9793,12 @@
         <f t="shared" si="3"/>
         <v>4.9167418254545465</v>
       </c>
+      <c r="N22">
+        <f t="shared" si="8"/>
+        <v>1.3800300000000001E-4</v>
+      </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -9661,8 +9816,12 @@
         <f t="shared" si="3"/>
         <v>4.2124845061538458</v>
       </c>
+      <c r="N23">
+        <f t="shared" si="8"/>
+        <v>1.3849049999999999E-4</v>
+      </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>14</v>
       </c>
@@ -9675,11 +9834,14 @@
       <c r="D24" t="s">
         <v>15</v>
       </c>
+      <c r="E24" t="s">
+        <v>3</v>
+      </c>
       <c r="F24" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2</v>
       </c>
@@ -9694,6 +9856,10 @@
         <f>C25*B25*1000</f>
         <v>1.0676820500000002</v>
       </c>
+      <c r="E25">
+        <f>(1.5*B25+0.4*0.2)/10000</f>
+        <v>1.4931500000000003E-5</v>
+      </c>
       <c r="F25" t="s">
         <v>11</v>
       </c>
@@ -9703,8 +9869,14 @@
       <c r="H25" t="s">
         <v>16</v>
       </c>
+      <c r="I25" t="s">
+        <v>3</v>
+      </c>
+      <c r="J25" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>4</v>
       </c>
@@ -9712,12 +9884,16 @@
         <v>9.0230000000000005E-2</v>
       </c>
       <c r="C26">
-        <f t="shared" ref="C26:C46" si="9">B26/A26</f>
+        <f t="shared" ref="C26:C46" si="12">B26/A26</f>
         <v>2.2557500000000001E-2</v>
       </c>
       <c r="D26">
-        <f t="shared" ref="D26:D46" si="10">C26*B26*1000</f>
+        <f t="shared" ref="D26:D46" si="13">C26*B26*1000</f>
         <v>2.0353632250000002</v>
+      </c>
+      <c r="E26">
+        <f>(1.5*B26+0.4*0.2)/10000</f>
+        <v>2.1534500000000002E-5</v>
       </c>
       <c r="F26">
         <v>1.8</v>
@@ -9728,8 +9904,16 @@
       <c r="H26">
         <v>0.10199999999999999</v>
       </c>
+      <c r="I26">
+        <f>(1.5*G26+0.4*200)/10000</f>
+        <v>8.1715999999999994E-3</v>
+      </c>
+      <c r="J26">
+        <f>(3*H26+200*0.5)/10000</f>
+        <v>1.0030599999999999E-2</v>
+      </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>10</v>
       </c>
@@ -9737,12 +9921,16 @@
         <v>0.22070000000000001</v>
       </c>
       <c r="C27">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2.2069999999999999E-2</v>
       </c>
       <c r="D27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>4.8708489999999998</v>
+      </c>
+      <c r="E27">
+        <f>(1.5*B27+0.3*2)/10000</f>
+        <v>9.3104999999999997E-5</v>
       </c>
       <c r="F27">
         <v>3.1</v>
@@ -9753,8 +9941,16 @@
       <c r="H27">
         <v>1.22</v>
       </c>
+      <c r="I27">
+        <f t="shared" ref="I27:I32" si="14">(1.5*G27+0.4*200)/10000</f>
+        <v>1.0022E-2</v>
+      </c>
+      <c r="J27">
+        <f t="shared" ref="J27:J32" si="15">(3*H27+200*0.5)/10000</f>
+        <v>1.0366E-2</v>
+      </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>16</v>
       </c>
@@ -9762,12 +9958,16 @@
         <v>0.33550000000000002</v>
       </c>
       <c r="C28">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2.0968750000000001E-2</v>
       </c>
       <c r="D28">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>7.0350156250000007</v>
+      </c>
+      <c r="E28">
+        <f t="shared" ref="E28:E45" si="16">(1.5*B28+0.3*2)/10000</f>
+        <v>1.1032500000000001E-4</v>
       </c>
       <c r="F28">
         <v>5.7</v>
@@ -9778,8 +9978,16 @@
       <c r="H28">
         <v>3.84</v>
       </c>
+      <c r="I28">
+        <f t="shared" si="14"/>
+        <v>1.3674500000000001E-2</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="15"/>
+        <v>1.1152E-2</v>
+      </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>30</v>
       </c>
@@ -9787,12 +9995,16 @@
         <v>0.45050000000000001</v>
       </c>
       <c r="C29">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1.5016666666666668E-2</v>
       </c>
       <c r="D29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>6.7650083333333342</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="16"/>
+        <v>1.27575E-4</v>
       </c>
       <c r="F29">
         <v>8.3000000000000007</v>
@@ -9803,8 +10015,16 @@
       <c r="H29">
         <v>6.6849999999999996</v>
       </c>
+      <c r="I29">
+        <f t="shared" si="14"/>
+        <v>1.6880000000000003E-2</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="15"/>
+        <v>1.2005500000000001E-2</v>
+      </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>60</v>
       </c>
@@ -9812,12 +10032,16 @@
         <v>0.49034</v>
       </c>
       <c r="C30">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>8.1723333333333335E-3</v>
       </c>
       <c r="D30">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>4.0072219266666673</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="16"/>
+        <v>1.3355100000000001E-4</v>
       </c>
       <c r="F30">
         <v>10.4</v>
@@ -9828,8 +10052,16 @@
       <c r="H30">
         <v>9.077</v>
       </c>
+      <c r="I30">
+        <f t="shared" si="14"/>
+        <v>1.8999499999999999E-2</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="15"/>
+        <v>1.2723099999999999E-2</v>
+      </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>120</v>
       </c>
@@ -9837,12 +10069,16 @@
         <v>0.50922000000000001</v>
       </c>
       <c r="C31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>4.2434999999999999E-3</v>
       </c>
       <c r="D31">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2.1608750699999999</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="16"/>
+        <v>1.3638300000000001E-4</v>
       </c>
       <c r="F31">
         <v>12.1</v>
@@ -9853,8 +10089,16 @@
       <c r="H31">
         <v>10.946</v>
       </c>
+      <c r="I31">
+        <f t="shared" si="14"/>
+        <v>2.0652499999999997E-2</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="15"/>
+        <v>1.32838E-2</v>
+      </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>230</v>
       </c>
@@ -9862,12 +10106,16 @@
         <v>0.51202999999999999</v>
       </c>
       <c r="C32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2.2262173913043478E-3</v>
       </c>
       <c r="D32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1.1398900908695651</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="16"/>
+        <v>1.3680450000000001E-4</v>
       </c>
       <c r="F32">
         <v>14.8</v>
@@ -9878,8 +10126,16 @@
       <c r="H32">
         <v>13.98</v>
       </c>
+      <c r="I32">
+        <f t="shared" si="14"/>
+        <v>2.2667000000000003E-2</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="15"/>
+        <v>1.4194E-2</v>
+      </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>20</v>
       </c>
@@ -9887,15 +10143,19 @@
         <v>0.38963999999999999</v>
       </c>
       <c r="C33">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1.9481999999999999E-2</v>
       </c>
       <c r="D33">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>7.5909664799999987</v>
       </c>
+      <c r="E33">
+        <f t="shared" si="16"/>
+        <v>1.1844600000000001E-4</v>
+      </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>25</v>
       </c>
@@ -9903,15 +10163,19 @@
         <v>0.4284</v>
       </c>
       <c r="C34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1.7135999999999998E-2</v>
       </c>
       <c r="D34">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>7.3410623999999993</v>
       </c>
+      <c r="E34">
+        <f t="shared" si="16"/>
+        <v>1.2425999999999998E-4</v>
+      </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>40</v>
       </c>
@@ -9919,15 +10183,19 @@
         <v>0.47216999999999998</v>
       </c>
       <c r="C35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1.1804249999999999E-2</v>
       </c>
       <c r="D35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>5.5736127224999992</v>
       </c>
+      <c r="E35">
+        <f t="shared" si="16"/>
+        <v>1.308255E-4</v>
+      </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>21</v>
       </c>
@@ -9935,15 +10203,19 @@
         <v>0.39887</v>
       </c>
       <c r="C36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1.8993809523809524E-2</v>
       </c>
       <c r="D36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>7.5760608047619042</v>
       </c>
+      <c r="E36">
+        <f t="shared" si="16"/>
+        <v>1.1983049999999999E-4</v>
+      </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>22</v>
       </c>
@@ -9951,15 +10223,19 @@
         <v>0.40751999999999999</v>
       </c>
       <c r="C37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1.8523636363636364E-2</v>
       </c>
       <c r="D37">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>7.5487522909090909</v>
       </c>
+      <c r="E37">
+        <f t="shared" si="16"/>
+        <v>1.21128E-4</v>
+      </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>23</v>
       </c>
@@ -9967,15 +10243,19 @@
         <v>0.41538000000000003</v>
       </c>
       <c r="C38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1.806E-2</v>
       </c>
       <c r="D38">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>7.5017628000000007</v>
       </c>
+      <c r="E38">
+        <f t="shared" si="16"/>
+        <v>1.2230699999999999E-4</v>
+      </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>24</v>
       </c>
@@ -9983,15 +10263,19 @@
         <v>0.42209000000000002</v>
       </c>
       <c r="C39">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1.7587083333333333E-2</v>
       </c>
       <c r="D39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>7.4233320041666664</v>
       </c>
+      <c r="E39">
+        <f t="shared" si="16"/>
+        <v>1.2331349999999998E-4</v>
+      </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>26</v>
       </c>
@@ -9999,15 +10283,19 @@
         <v>0.43289</v>
       </c>
       <c r="C40">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1.6649615384615384E-2</v>
       </c>
       <c r="D40">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>7.2074520038461536</v>
       </c>
+      <c r="E40">
+        <f t="shared" si="16"/>
+        <v>1.2493349999999999E-4</v>
+      </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>19</v>
       </c>
@@ -10015,15 +10303,19 @@
         <v>0.37761</v>
       </c>
       <c r="C41">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1.9874210526315789E-2</v>
       </c>
       <c r="D41">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>7.5047006368421059</v>
       </c>
+      <c r="E41">
+        <f t="shared" si="16"/>
+        <v>1.166415E-4</v>
+      </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>18</v>
       </c>
@@ -10031,15 +10323,19 @@
         <v>0.36514999999999997</v>
       </c>
       <c r="C42">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2.0286111111111109E-2</v>
       </c>
       <c r="D42">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>7.4074734722222209</v>
       </c>
+      <c r="E42">
+        <f t="shared" si="16"/>
+        <v>1.1477249999999999E-4</v>
+      </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>17</v>
       </c>
@@ -10047,15 +10343,19 @@
         <v>0.35048000000000001</v>
       </c>
       <c r="C43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2.0616470588235295E-2</v>
       </c>
       <c r="D43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>7.2256606117647069</v>
       </c>
+      <c r="E43">
+        <f t="shared" si="16"/>
+        <v>1.1257199999999998E-4</v>
+      </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>15</v>
       </c>
@@ -10063,15 +10363,19 @@
         <v>0.31845000000000001</v>
       </c>
       <c r="C44">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2.1230000000000002E-2</v>
       </c>
       <c r="D44">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>6.7606935000000012</v>
       </c>
+      <c r="E44">
+        <f t="shared" si="16"/>
+        <v>1.0776749999999999E-4</v>
+      </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>12</v>
       </c>
@@ -10079,15 +10383,19 @@
         <v>0.26246000000000003</v>
       </c>
       <c r="C45">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2.1871666666666668E-2</v>
       </c>
       <c r="D45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>5.7404376333333342</v>
       </c>
+      <c r="E45">
+        <f t="shared" si="16"/>
+        <v>9.936899999999999E-5</v>
+      </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>6</v>
       </c>
@@ -10095,12 +10403,16 @@
         <v>0.13444</v>
       </c>
       <c r="C46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2.2406666666666668E-2</v>
       </c>
       <c r="D46">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>3.0123522666666669</v>
+      </c>
+      <c r="E46">
+        <f>(1.5*B46+0.4*200)/10000</f>
+        <v>8.0201660000000004E-3</v>
       </c>
     </row>
   </sheetData>

--- a/uloha28/uloha28.xlsx
+++ b/uloha28/uloha28.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nemec\david\school\praktika\uloha28\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A44B0351-7630-4C1E-91A2-E4ED5FED4A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFED3B96-D3A3-4A8F-959C-B6CF845545A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{168F654F-1575-4592-821A-2A29CD728C13}"/>
   </bookViews>

--- a/uloha28/uloha28.xlsx
+++ b/uloha28/uloha28.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nemec\david\school\praktika\uloha28\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFED3B96-D3A3-4A8F-959C-B6CF845545A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC57E9B-5498-42C4-AD5A-C69511AA968F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{168F654F-1575-4592-821A-2A29CD728C13}"/>
   </bookViews>
@@ -10411,8 +10411,8 @@
         <v>3.0123522666666669</v>
       </c>
       <c r="E46">
-        <f>(1.5*B46+0.4*200)/10000</f>
-        <v>8.0201660000000004E-3</v>
+        <f>(1.5*B46+0.4*0.2)/10000</f>
+        <v>2.8166000000000001E-5</v>
       </c>
     </row>
   </sheetData>

--- a/uloha28/uloha28.xlsx
+++ b/uloha28/uloha28.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nemec\david\school\praktika\uloha28\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC57E9B-5498-42C4-AD5A-C69511AA968F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00EF4514-6908-477C-A0A0-994BDC76A732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{168F654F-1575-4592-821A-2A29CD728C13}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="18">
   <si>
     <t>P/Psun</t>
   </si>
@@ -3407,6 +3407,21 @@
               <a:effectLst/>
             </c:spPr>
             <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="2"/>
             <c:dispRSqr val="0"/>
             <c:dispEq val="0"/>
           </c:trendline>
@@ -9543,6 +9558,9 @@
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>0</v>
+      </c>
       <c r="B18" t="s">
         <v>1</v>
       </c>
@@ -9596,8 +9614,8 @@
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>5</v>
+      <c r="A19">
+        <v>0.25</v>
       </c>
       <c r="B19">
         <f>B5</f>
@@ -9657,8 +9675,8 @@
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>6</v>
+      <c r="A20">
+        <v>0.5</v>
       </c>
       <c r="B20">
         <f>B8</f>
@@ -9718,8 +9736,8 @@
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>7</v>
+      <c r="A21">
+        <v>1</v>
       </c>
       <c r="B21">
         <f>B13</f>
